--- a/results/02_taxa_assemblage/LDA_Method/ModelD_AllSites/tables/confusion_matrix_unified.xlsx
+++ b/results/02_taxa_assemblage/LDA_Method/ModelD_AllSites/tables/confusion_matrix_unified.xlsx
@@ -431,7 +431,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Part 1: Training Resubstitution — Core (n=35) + Peripheral (n=10) + Uncertain (n=5)</t>
+          <t>Part 1: Training Resubstitution — Core (n=25) + Peripheral (n=23) + Uncertain (n=2)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr"/>
@@ -469,16 +469,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>63</v>
+        <v>90</v>
       </c>
       <c r="C3" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -488,16 +488,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -507,16 +507,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="C5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -526,16 +526,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="C6" t="n">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="D6" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E6" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -548,7 +548,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Part 2: 5-Fold x 10 Cross-Validation — Core (n=35) + Peripheral (n=10) + Uncertain (n=5)</t>
+          <t>Part 2: 5-Fold x 10 Cross-Validation — Core (n=25) + Peripheral (n=23) + Uncertain (n=2)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -586,16 +586,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>84</v>
       </c>
       <c r="C10" t="n">
-        <v>118</v>
+        <v>259</v>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="E10" t="n">
-        <v>56</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11">
@@ -605,16 +605,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="C11" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D11" t="n">
         <v>62</v>
       </c>
       <c r="E11" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -624,16 +624,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D12" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>55</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13">
@@ -643,16 +643,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="C13" t="n">
-        <v>231</v>
+        <v>371</v>
       </c>
       <c r="D13" t="n">
-        <v>115</v>
+        <v>96</v>
       </c>
       <c r="E13" t="n">
-        <v>154</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
